--- a/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57501</t>
+          <t>59337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30537</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51670</t>
+          <t>52385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>55393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99453</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56364</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85383</t>
+          <t>85565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72960</t>
+          <t>72712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96515</t>
+          <t>95808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135576</t>
+          <t>135267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173469</t>
+          <t>173508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64059</t>
+          <t>64971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94805</t>
+          <t>94443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68513</t>
+          <t>68364</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90952</t>
+          <t>91792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139430</t>
+          <t>138956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>178322</t>
+          <t>179158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44143</t>
+          <t>42253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72032</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56777</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31536</t>
+          <t>30763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50058</t>
+          <t>49468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69614</t>
+          <t>71023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99700</t>
+          <t>99028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>53283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53230</t>
+          <t>55655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96912</t>
+          <t>97017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94265</t>
+          <t>93875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88746</t>
+          <t>88732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120890</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157949</t>
+          <t>157145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205247</t>
+          <t>205199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140694</t>
+          <t>143121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185732</t>
+          <t>188327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108634</t>
+          <t>111207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141478</t>
+          <t>140576</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>260509</t>
+          <t>264362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>314909</t>
+          <t>317254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42879</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>69436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>73957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100251</t>
+          <t>98154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136344</t>
+          <t>134732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>26426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49670</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31576</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>50846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>61644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92853</t>
+          <t>92917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48667</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75163</t>
+          <t>72550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45042</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76705</t>
+          <t>76766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142644</t>
+          <t>142550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379633</t>
+          <t>380454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189167</t>
+          <t>189917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>532808</t>
+          <t>540036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91080</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124866</t>
+          <t>125368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149777</t>
+          <t>146787</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>76768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270896</t>
+          <t>270438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19357</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84837</t>
+          <t>86917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>36817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72893</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59900</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30614</t>
+          <t>30798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>43905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79205</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61308</t>
+          <t>62113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93876</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106527</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136540</t>
+          <t>137421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>175900</t>
+          <t>175055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>222067</t>
+          <t>219328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119789</t>
+          <t>120919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157986</t>
+          <t>158400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>134565</t>
+          <t>135959</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>168861</t>
+          <t>168490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>266677</t>
+          <t>266201</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>316729</t>
+          <t>318628</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54180</t>
+          <t>55223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85277</t>
+          <t>87775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>47216</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70511</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108160</t>
+          <t>108281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148534</t>
+          <t>147523</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>40441</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66697</t>
+          <t>68182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>67419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96800</t>
+          <t>94585</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116805</t>
+          <t>114864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>154009</t>
+          <t>154608</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99971</t>
+          <t>100104</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163995</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75302</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149638</t>
+          <t>151828</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>195872</t>
+          <t>195522</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>296553</t>
+          <t>296322</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>248583</t>
+          <t>252177</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>313491</t>
+          <t>317602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>440661</t>
+          <t>439397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>913501</t>
+          <t>890283</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>710318</t>
+          <t>709346</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1333496</t>
+          <t>1353989</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>450314</t>
+          <t>452150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>527014</t>
+          <t>531702</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>282932</t>
+          <t>278057</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>508186</t>
+          <t>506462</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>702130</t>
+          <t>692803</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1014349</t>
+          <t>1011986</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>160164</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>211053</t>
+          <t>212122</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111439</t>
+          <t>111466</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>208890</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>270599</t>
+          <t>278263</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>400077</t>
+          <t>401916</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>133150</t>
+          <t>135529</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>184790</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>112928</t>
+          <t>120102</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>219008</t>
+          <t>219843</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>264235</t>
+          <t>260708</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>379795</t>
+          <t>384272</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59337</t>
+          <t>52217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40279</t>
+          <t>42238</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>33699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>54505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>71025</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55393</t>
+          <t>57224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95761</t>
+          <t>95087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70648</t>
+          <t>81143</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85565</t>
+          <t>99989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>90737</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72712</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95808</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>154487</t>
+          <t>171880</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135267</t>
+          <t>151689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173508</t>
+          <t>192623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>83297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64971</t>
+          <t>68879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94443</t>
+          <t>99996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>84541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68364</t>
+          <t>71878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91792</t>
+          <t>97243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>158132</t>
+          <t>167838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>138956</t>
+          <t>149738</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179158</t>
+          <t>190974</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>49079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>37483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58270</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>51683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70570</t>
+          <t>81841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>47873</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56118</t>
+          <t>60798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>43965</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>34459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49468</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>83830</t>
+          <t>91838</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>75805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>109848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>255657</t>
+          <t>278606</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>255657</t>
+          <t>278606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>255657</t>
+          <t>278606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>270086</t>
+          <t>290093</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>270086</t>
+          <t>290093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>270086</t>
+          <t>290093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>525743</t>
+          <t>568699</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>525743</t>
+          <t>568699</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>525743</t>
+          <t>568699</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>41302</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52656</t>
+          <t>56807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73506</t>
+          <t>73373</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55655</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97017</t>
+          <t>95344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>89208</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59958</t>
+          <t>71010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93875</t>
+          <t>108330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>103677</t>
+          <t>119977</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>103760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119569</t>
+          <t>138228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>179554</t>
+          <t>209185</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157145</t>
+          <t>186762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205199</t>
+          <t>236524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163061</t>
+          <t>173006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143121</t>
+          <t>152160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>188327</t>
+          <t>192626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>135519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111207</t>
+          <t>118614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140576</t>
+          <t>151544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>288691</t>
+          <t>308525</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>264362</t>
+          <t>284366</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>317254</t>
+          <t>337405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>61008</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42451</t>
+          <t>47848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61731</t>
+          <t>69211</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>56365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73957</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>116717</t>
+          <t>130218</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98154</t>
+          <t>112318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>152767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36206</t>
+          <t>41575</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26426</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>57830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>46543</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>59157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>88119</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>72679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92917</t>
+          <t>105951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>364959</t>
+          <t>396868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>364959</t>
+          <t>396868</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>364959</t>
+          <t>396868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>369461</t>
+          <t>412552</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>369461</t>
+          <t>412552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>369461</t>
+          <t>412552</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>734419</t>
+          <t>809420</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>734419</t>
+          <t>809420</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>734419</t>
+          <t>809420</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46837</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>54780</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>40944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60762</t>
+          <t>72451</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45345</t>
+          <t>55750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76766</t>
+          <t>89975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>283630</t>
+          <t>100370</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142550</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380454</t>
+          <t>116230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>344392</t>
+          <t>172822</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189917</t>
+          <t>149512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540036</t>
+          <t>196537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107268</t>
+          <t>116840</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>99025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125368</t>
+          <t>134880</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73969</t>
+          <t>84351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146787</t>
+          <t>97580</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>181237</t>
+          <t>201192</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76768</t>
+          <t>178067</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270438</t>
+          <t>222740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>31500</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58943</t>
+          <t>41243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>61466</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86917</t>
+          <t>77430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36817</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73542</t>
+          <t>63432</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>244996</t>
+          <t>271874</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244996</t>
+          <t>271874</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>244996</t>
+          <t>271874</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>428721</t>
+          <t>265773</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>428721</t>
+          <t>265773</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>428721</t>
+          <t>265773</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>673717</t>
+          <t>537647</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>673717</t>
+          <t>537647</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>673717</t>
+          <t>537647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>25019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57516</t>
+          <t>54451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20386</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>58330</t>
+          <t>63855</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>47985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78704</t>
+          <t>82231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>76056</t>
+          <t>90346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62113</t>
+          <t>72084</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>121861</t>
+          <t>132757</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105616</t>
+          <t>115502</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137421</t>
+          <t>150892</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>197917</t>
+          <t>223103</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>175055</t>
+          <t>195169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>219328</t>
+          <t>248339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139167</t>
+          <t>144779</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120919</t>
+          <t>124553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>158400</t>
+          <t>163808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>151885</t>
+          <t>160550</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135959</t>
+          <t>142661</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>168490</t>
+          <t>179143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>291052</t>
+          <t>305329</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>266201</t>
+          <t>278289</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>318628</t>
+          <t>332747</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>76566</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87775</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>57756</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47216</t>
+          <t>50317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>75983</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>127393</t>
+          <t>138311</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108281</t>
+          <t>119154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>163010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>60358</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40441</t>
+          <t>47578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68182</t>
+          <t>77289</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>93167</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67419</t>
+          <t>78060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94585</t>
+          <t>110641</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>134094</t>
+          <t>153524</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114864</t>
+          <t>133514</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>154608</t>
+          <t>177480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>376039</t>
+          <t>409750</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>376039</t>
+          <t>409750</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>376039</t>
+          <t>409750</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>432747</t>
+          <t>474371</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>432747</t>
+          <t>474371</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>432747</t>
+          <t>474371</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>808785</t>
+          <t>884122</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>808785</t>
+          <t>884122</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>808785</t>
+          <t>884122</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>128454</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100104</t>
+          <t>102008</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>162206</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>116416</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151828</t>
+          <t>158367</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>249995</t>
+          <t>264735</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>195522</t>
+          <t>232760</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>296322</t>
+          <t>303362</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>283343</t>
+          <t>333148</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>252177</t>
+          <t>301118</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>317602</t>
+          <t>368133</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>593006</t>
+          <t>443842</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>439397</t>
+          <t>412819</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>890283</t>
+          <t>477928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>876349</t>
+          <t>776990</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>709346</t>
+          <t>731268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1353989</t>
+          <t>823405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>488377</t>
+          <t>517923</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>452150</t>
+          <t>481749</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>531702</t>
+          <t>558061</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>430735</t>
+          <t>464961</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>278057</t>
+          <t>432223</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>506462</t>
+          <t>494134</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>919112</t>
+          <t>982883</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>692803</t>
+          <t>933651</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1011986</t>
+          <t>1032145</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>184430</t>
+          <t>203344</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>160164</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>212122</t>
+          <t>234296</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>173576</t>
+          <t>191067</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111466</t>
+          <t>169281</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>214024</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>358005</t>
+          <t>394411</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>278263</t>
+          <t>364463</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>401916</t>
+          <t>433554</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>157048</t>
+          <t>174468</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>135529</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>184790</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>182156</t>
+          <t>206400</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>120102</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>219843</t>
+          <t>230343</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>339203</t>
+          <t>380868</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>260708</t>
+          <t>351474</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>384272</t>
+          <t>417216</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
